--- a/Evaluation1/testing result/Usability_Test_Results.xlsx
+++ b/Evaluation1/testing result/Usability_Test_Results.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wen/uq/deco7230/Prototype1_BurstDebugInformation_DoNotShip/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wen/uq/deco7230/DECO7230_JIEWEN_2026/Evaluation1/testing result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23294E95-0F9E-944C-93B8-FA321D1DCF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE18BDB5-A401-054C-8E28-F97CD3FC0190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="27820" windowHeight="17140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1120" windowWidth="27820" windowHeight="17140" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Results" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Test Results" sheetId="1" r:id="rId1"/>
     <sheet name="P1" sheetId="2" r:id="rId2"/>
     <sheet name="P2" sheetId="3" r:id="rId3"/>
     <sheet name="P3" sheetId="4" r:id="rId4"/>
@@ -25,121 +25,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>Task 1: 理解
-空间区域</t>
-  </si>
-  <si>
-    <t>Task 2: 把问
-题卡片从
-Unsorted 移到
-Problems</t>
-  </si>
-  <si>
-    <t>完成时间</t>
-  </si>
-  <si>
-    <t>是否需要提示</t>
-  </si>
-  <si>
-    <t>错误/犹豫</t>
-  </si>
-  <si>
-    <t>Task 3: 理解
-整体用途</t>
-  </si>
-  <si>
-    <t>整体评价 /5</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
-    <t>正确理解 Unsorted 和 Problems</t>
-  </si>
-  <si>
-    <t>成功</t>
-  </si>
-  <si>
-    <t>18s</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>无明显错误</t>
-  </si>
-  <si>
-    <t>能准确解释“整理和分类想法”</t>
-  </si>
-  <si>
     <t>P2</t>
   </si>
   <si>
-    <t>正确理解两个区域</t>
-  </si>
-  <si>
-    <t>24s</t>
-  </si>
-  <si>
-    <t>第一次稍微犹豫怎么移动物体</t>
-  </si>
-  <si>
-    <t>能理解大量信息可按类别整理</t>
-  </si>
-  <si>
     <t>P3</t>
   </si>
   <si>
-    <t>基本理解，但一开始不确定 Problems 是“问题”还是“待处理事项”</t>
-  </si>
-  <si>
-    <t>31s</t>
-  </si>
-  <si>
-    <t>在两个区域之间观察约 6s</t>
-  </si>
-  <si>
-    <t>能正确解释系统用途</t>
-  </si>
-  <si>
     <t>P4</t>
   </si>
   <si>
-    <t>正确理解区域</t>
-  </si>
-  <si>
-    <t>21s</t>
-  </si>
-  <si>
-    <t>首次交互前短暂停顿</t>
-  </si>
-  <si>
-    <t>能理解空间分类逻辑</t>
-  </si>
-  <si>
     <t>P5</t>
   </si>
   <si>
-    <t>能理解 Unsorted，但没有马上发现卡片可以移动</t>
-  </si>
-  <si>
-    <t>37s</t>
-  </si>
-  <si>
-    <t>是，1次轻微提示</t>
-  </si>
-  <si>
-    <t>不确定如何开始操作</t>
-  </si>
-  <si>
-    <t>提示后完全理解系统逻辑</t>
-  </si>
-  <si>
     <t>P1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -217,6 +122,178 @@
   </si>
   <si>
     <t>For now it's clear with the instructions. Maybe one thing I will suggest is to add multi selection features, allow us to select multiple notes and hold them together at one time. Now we can only do this one by one, and it's time-consuming. Most time we can decide several notes all belongs to one category and be able to move them together will be nice, more convenient.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2min14s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1min23s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2min44s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1min</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3min15s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Correctly Understanding Unsorted and Problems</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Correctly Understanding Zones</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Got the basic idea, but at first not sure if 'Problems' meant 'actual problems' or 'pending tasks'.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish time</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>error/hesitate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Understood 'Unsorted', but not immediately realize that the cards could be moved.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>success</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>require help？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yes, 1 gentle nudge.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No obvious errors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hesitated slightly the first time I tried to move the object.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Looked back and forth between the two zones for about 6s.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brief pause before the first interaction.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unsure how to get started.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can accurately explain 'organizing and categorizing ideas'.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can correctly explain the system's purpose.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Understands that large amounts of information can be organized by category.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Understands the spatial categorization logic.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fully understands the system logic after being prompted.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall Assessment/5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Task 3: Understands the overall purpose</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Task 1: Understands the spatial zones</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Task 2: Move the problem card from Unsorted to Problems</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mostly yes. I understood that I needed to organise the cards, but at first I wasn’t completely sure what “Problems” meant.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>It was fairly easy after I understood what each zone represented. I needed a few seconds to compare the zones before deciding.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The layout was clear, but the label “Problems” was a little ambiguous to me. I first thought it might mean tasks that still needed to be completed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I expected to be able to pick up the card and move it into the appropriate area.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maybe add a short description or example under each category label so users can understand the meaning of the zones immediately.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yes, it was quite clear that I needed to move the card into the correct category.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Very easy. The different areas made the categorisation clear.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not really. The labels and layout were straightforward.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I expected the card to be picked up and then placed on the selected board.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maybe add a small visual highlight when a card can be picked up or when I am close enough to a board to place it.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I understood that the cards needed to be organised, but at first I wasn’t sure how to start interacting with them.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The categories were understandable, but figuring out how to move the card was more difficult than deciding where it should go.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The labels were mostly clear. The confusing part was that I didn’t immediately realise the cards were interactive and could be moved.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>At first I expected some instruction or button to appear telling me how to interact with the card. After the hint, I understood that I could pick it up and move it.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add a visible interaction prompt, such as “Press E to pick up”, or highlight the card when the user gets close to it.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -224,7 +301,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +322,14 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -288,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -298,6 +383,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,7 +703,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="24.5" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="25" customWidth="1"/>
@@ -617,153 +714,153 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="45">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="30">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H2" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:8" ht="60">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H3" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="45">
+    <row r="4" spans="1:8" ht="75">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15">
+    <row r="5" spans="1:8" ht="30">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H5" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30">
+    <row r="6" spans="1:8" ht="60">
       <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="H6" s="2">
         <v>4</v>
@@ -785,47 +882,47 @@
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28" customHeight="1">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28" customHeight="1">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28" customHeight="1">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28" customHeight="1">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28" customHeight="1">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28" customHeight="1"/>
@@ -878,51 +975,52 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="67.33203125" customWidth="1"/>
+    <col min="2" max="2" width="124.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1">
       <c r="A1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="28" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="27" customHeight="1">
       <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="28" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="45" customHeight="1">
       <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="28" customHeight="1">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="37" customHeight="1">
       <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28" customHeight="1">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31" customHeight="1">
       <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="28" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="69" customHeight="1">
       <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28" customHeight="1"/>
@@ -971,52 +1069,68 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B6B27F-F00A-E94F-B373-732E710F7761}">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="67.33203125" customWidth="1"/>
+    <col min="2" max="2" width="80.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28" customHeight="1">
+    <row r="1" spans="1:2" ht="28" customHeight="1">
       <c r="A1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="28" customHeight="1">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="28" customHeight="1">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="28" customHeight="1">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="28" customHeight="1">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="28" customHeight="1">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="28" customHeight="1"/>
-    <row r="8" spans="1:1" ht="28" customHeight="1"/>
-    <row r="9" spans="1:1" ht="28" customHeight="1"/>
-    <row r="10" spans="1:1" ht="28" customHeight="1"/>
-    <row r="11" spans="1:1" ht="28" customHeight="1"/>
-    <row r="12" spans="1:1" ht="28" customHeight="1"/>
-    <row r="13" spans="1:1" ht="28" customHeight="1"/>
-    <row r="14" spans="1:1" ht="28" customHeight="1"/>
-    <row r="15" spans="1:1" ht="28" customHeight="1"/>
-    <row r="16" spans="1:1" ht="28" customHeight="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="42" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="42" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="42" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="42" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28" customHeight="1"/>
+    <row r="8" spans="1:2" ht="28" customHeight="1"/>
+    <row r="9" spans="1:2" ht="28" customHeight="1"/>
+    <row r="10" spans="1:2" ht="28" customHeight="1"/>
+    <row r="11" spans="1:2" ht="28" customHeight="1"/>
+    <row r="12" spans="1:2" ht="28" customHeight="1"/>
+    <row r="13" spans="1:2" ht="28" customHeight="1"/>
+    <row r="14" spans="1:2" ht="28" customHeight="1"/>
+    <row r="15" spans="1:2" ht="28" customHeight="1"/>
+    <row r="16" spans="1:2" ht="28" customHeight="1"/>
     <row r="17" ht="28" customHeight="1"/>
     <row r="18" ht="28" customHeight="1"/>
     <row r="19" ht="28" customHeight="1"/>
@@ -1053,52 +1167,73 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0F2621-A7B3-D549-9D13-F463720961EC}">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="67.33203125" customWidth="1"/>
+    <col min="2" max="2" width="85.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28" customHeight="1">
+    <row r="1" spans="1:3" ht="28" customHeight="1">
       <c r="A1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="28" customHeight="1">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="28" customHeight="1">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="28" customHeight="1">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="28" customHeight="1">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="28" customHeight="1">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="28" customHeight="1"/>
-    <row r="8" spans="1:1" ht="28" customHeight="1"/>
-    <row r="9" spans="1:1" ht="28" customHeight="1"/>
-    <row r="10" spans="1:1" ht="28" customHeight="1"/>
-    <row r="11" spans="1:1" ht="28" customHeight="1"/>
-    <row r="12" spans="1:1" ht="28" customHeight="1"/>
-    <row r="13" spans="1:1" ht="28" customHeight="1"/>
-    <row r="14" spans="1:1" ht="28" customHeight="1"/>
-    <row r="15" spans="1:1" ht="28" customHeight="1"/>
-    <row r="16" spans="1:1" ht="28" customHeight="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="51" customHeight="1">
+      <c r="A2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" spans="1:3" ht="51" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" ht="51" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:3" ht="51" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:3" ht="51" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:3" ht="28" customHeight="1"/>
+    <row r="8" spans="1:3" ht="28" customHeight="1"/>
+    <row r="9" spans="1:3" ht="28" customHeight="1"/>
+    <row r="10" spans="1:3" ht="28" customHeight="1"/>
+    <row r="11" spans="1:3" ht="28" customHeight="1"/>
+    <row r="12" spans="1:3" ht="28" customHeight="1"/>
+    <row r="13" spans="1:3" ht="28" customHeight="1"/>
+    <row r="14" spans="1:3" ht="28" customHeight="1"/>
+    <row r="15" spans="1:3" ht="28" customHeight="1"/>
+    <row r="16" spans="1:3" ht="28" customHeight="1"/>
     <row r="17" ht="28" customHeight="1"/>
     <row r="18" ht="28" customHeight="1"/>
     <row r="19" ht="28" customHeight="1"/>
@@ -1135,52 +1270,68 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8814D8EC-F1B1-3443-801D-2CD73A3F40D3}">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="67.33203125" customWidth="1"/>
+    <col min="2" max="2" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28" customHeight="1">
+    <row r="1" spans="1:2" ht="28" customHeight="1">
       <c r="A1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="28" customHeight="1">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="28" customHeight="1">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="28" customHeight="1">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="28" customHeight="1">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="28" customHeight="1">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="28" customHeight="1"/>
-    <row r="8" spans="1:1" ht="28" customHeight="1"/>
-    <row r="9" spans="1:1" ht="28" customHeight="1"/>
-    <row r="10" spans="1:1" ht="28" customHeight="1"/>
-    <row r="11" spans="1:1" ht="28" customHeight="1"/>
-    <row r="12" spans="1:1" ht="28" customHeight="1"/>
-    <row r="13" spans="1:1" ht="28" customHeight="1"/>
-    <row r="14" spans="1:1" ht="28" customHeight="1"/>
-    <row r="15" spans="1:1" ht="28" customHeight="1"/>
-    <row r="16" spans="1:1" ht="28" customHeight="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
+      <c r="A2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28" customHeight="1"/>
+    <row r="8" spans="1:2" ht="28" customHeight="1"/>
+    <row r="9" spans="1:2" ht="28" customHeight="1"/>
+    <row r="10" spans="1:2" ht="28" customHeight="1"/>
+    <row r="11" spans="1:2" ht="28" customHeight="1"/>
+    <row r="12" spans="1:2" ht="28" customHeight="1"/>
+    <row r="13" spans="1:2" ht="28" customHeight="1"/>
+    <row r="14" spans="1:2" ht="28" customHeight="1"/>
+    <row r="15" spans="1:2" ht="28" customHeight="1"/>
+    <row r="16" spans="1:2" ht="28" customHeight="1"/>
     <row r="17" ht="28" customHeight="1"/>
     <row r="18" ht="28" customHeight="1"/>
     <row r="19" ht="28" customHeight="1"/>

--- a/Evaluation1/testing result/Usability_Test_Results.xlsx
+++ b/Evaluation1/testing result/Usability_Test_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wen/uq/deco7230/DECO7230_JIEWEN_2026/Evaluation1/testing result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE18BDB5-A401-054C-8E28-F97CD3FC0190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE34C97-6942-7045-8D1E-758EB0D7CF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1120" windowWidth="27820" windowHeight="17140" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="27820" windowHeight="17140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Results" sheetId="1" r:id="rId1"/>
@@ -173,10 +173,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>require help？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>yes, 1 gentle nudge.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -294,6 +290,23 @@
   </si>
   <si>
     <t>Add a visible interaction prompt, such as “Press E to pick up”, or highlight the card when the user gets close to it.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>require help</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -301,7 +314,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,6 +327,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -327,12 +341,17 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -343,6 +362,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4F81BD"/>
         <bgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -356,16 +381,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFDDDDDD"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFDDDDDD"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFDDDDDD"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFDDDDDD"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -373,28 +398,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -710,159 +743,159 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="60">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="45">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="45">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="45">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="60">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="45">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="60">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="75">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="60">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>4</v>
       </c>
     </row>
@@ -874,67 +907,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{645D02BB-072A-4541-9C86-C7DA4BD62172}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="67.33203125" customWidth="1"/>
+    <col min="2" max="2" width="53.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28" customHeight="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" ht="28" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="28" customHeight="1">
-      <c r="A2" t="s">
+      <c r="B1" s="10"/>
+    </row>
+    <row r="2" spans="1:2" ht="28" customHeight="1">
+      <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28" customHeight="1">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="28" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28" customHeight="1">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="28" customHeight="1">
+      <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="28" customHeight="1">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="28" customHeight="1">
+      <c r="A5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="28" customHeight="1">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="28" customHeight="1">
+      <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="28" customHeight="1"/>
-    <row r="8" spans="1:3" ht="28" customHeight="1"/>
-    <row r="9" spans="1:3" ht="28" customHeight="1"/>
-    <row r="10" spans="1:3" ht="28" customHeight="1"/>
-    <row r="11" spans="1:3" ht="28" customHeight="1"/>
-    <row r="12" spans="1:3" ht="28" customHeight="1"/>
-    <row r="13" spans="1:3" ht="28" customHeight="1"/>
-    <row r="14" spans="1:3" ht="28" customHeight="1"/>
-    <row r="15" spans="1:3" ht="28" customHeight="1"/>
-    <row r="16" spans="1:3" ht="28" customHeight="1"/>
+    <row r="7" spans="1:2" ht="28" customHeight="1"/>
+    <row r="8" spans="1:2" ht="28" customHeight="1"/>
+    <row r="9" spans="1:2" ht="28" customHeight="1"/>
+    <row r="10" spans="1:2" ht="28" customHeight="1"/>
+    <row r="11" spans="1:2" ht="28" customHeight="1"/>
+    <row r="12" spans="1:2" ht="28" customHeight="1"/>
+    <row r="13" spans="1:2" ht="28" customHeight="1"/>
+    <row r="14" spans="1:2" ht="28" customHeight="1"/>
+    <row r="15" spans="1:2" ht="28" customHeight="1"/>
+    <row r="16" spans="1:2" ht="28" customHeight="1"/>
     <row r="17" ht="28" customHeight="1"/>
     <row r="18" ht="28" customHeight="1"/>
     <row r="19" ht="28" customHeight="1"/>
@@ -979,47 +1014,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1">
-      <c r="A1" t="s">
+      <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:2" ht="27" customHeight="1">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" customHeight="1">
-      <c r="A3" t="s">
+      <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="37" customHeight="1">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31" customHeight="1">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="69" customHeight="1">
-      <c r="A6" t="s">
+      <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1077,48 +1113,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1">
-      <c r="A1" t="s">
+      <c r="A1" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="42" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="42" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="4" spans="1:2" ht="42" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="42" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7" t="s">
+    <row r="5" spans="1:2" ht="42" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="42" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="7" t="s">
+    <row r="6" spans="1:2" ht="42" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="42" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28" customHeight="1"/>
@@ -1175,54 +1212,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1">
-      <c r="A1" t="s">
+      <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:3" ht="51" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="51" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" ht="51" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="51" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="6"/>
-    </row>
-    <row r="4" spans="1:3" ht="51" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="51" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:3" ht="51" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" ht="51" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" spans="1:3" ht="51" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" ht="28" customHeight="1"/>
     <row r="8" spans="1:3" ht="28" customHeight="1"/>
@@ -1278,48 +1316,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1">
-      <c r="A1" t="s">
+      <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="5"/>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="63" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="63" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="63" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7" t="s">
+    <row r="5" spans="1:2" s="1" customFormat="1" ht="63" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="7" t="s">
+    <row r="6" spans="1:2" s="1" customFormat="1" ht="63" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="6" customFormat="1" ht="63" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28" customHeight="1"/>
